--- a/InputData/fuels/PEIIR/Pollutant Emissions Intensity Improvement Rate.xlsx
+++ b/InputData/fuels/PEIIR/Pollutant Emissions Intensity Improvement Rate.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\fuels\PEIIR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\fuels\PEIIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E3BD0C-A423-4B33-9496-E16F34203A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="135" windowWidth="19425" windowHeight="10740" tabRatio="783"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="783" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -21,14 +22,7 @@
     <sheet name="PEIIR-TFPEIIR-motorbikes" sheetId="13" r:id="rId7"/>
     <sheet name="PEIIR-EFPEIIR" sheetId="6" r:id="rId8"/>
     <sheet name="PEIIR-BFPEIIR" sheetId="7" r:id="rId9"/>
-    <sheet name="PEIIR-IFPEIIR-cement" sheetId="19" r:id="rId10"/>
-    <sheet name="PEIIR-IFPEIIR-ngps" sheetId="20" r:id="rId11"/>
-    <sheet name="PEIIR-IFPEIIR-steel" sheetId="24" r:id="rId12"/>
-    <sheet name="PEIIR-IFPEIIR-chemicals" sheetId="21" r:id="rId13"/>
-    <sheet name="PEIIR-IFPEIIR-mining" sheetId="22" r:id="rId14"/>
-    <sheet name="PEIIR-IFPEIIR-waste-mgmt" sheetId="25" r:id="rId15"/>
-    <sheet name="PEIIR-IFPEIIR-agriculture" sheetId="23" r:id="rId16"/>
-    <sheet name="PEIIR-IFPEIIR-other-industries" sheetId="26" r:id="rId17"/>
+    <sheet name="PEIIR-IFPEIIR" sheetId="19" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="BTU_per_kWh">About!#REF!</definedName>
@@ -40,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="74">
   <si>
     <t>Source:</t>
   </si>
@@ -124,9 +118,6 @@
   </si>
   <si>
     <t>jet fuel</t>
-  </si>
-  <si>
-    <t>natural gas nonpeaker</t>
   </si>
   <si>
     <t>geothermal</t>
@@ -262,11 +253,38 @@
   <si>
     <t>Improvement Rate (dimensionless)</t>
   </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -334,23 +352,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -363,8 +374,8 @@
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 21" xfId="1"/>
-    <cellStyle name="Normal 40" xfId="2"/>
+    <cellStyle name="Normal 21" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 40" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -385,9 +396,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -425,9 +436,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -462,7 +473,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -497,7 +508,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -670,135 +681,135 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.73046875" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="73" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A23" s="1" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -808,60 +819,60 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="A1" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
+      <c r="H1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -896,7 +907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -931,7 +942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -966,7 +977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1001,7 +1012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1036,7 +1047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1071,7 +1082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1106,7 +1117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1141,7 +1152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1176,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1211,7 +1222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1246,3367 +1257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -4648,61 +1299,61 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.265625" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="21.3984375" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="7" max="7" width="16.59765625" customWidth="1"/>
-    <col min="8" max="8" width="11.1328125" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" customWidth="1"/>
-    <col min="10" max="10" width="13.1328125" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4737,7 +1388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4772,7 +1423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4807,7 +1458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4842,7 +1493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4877,7 +1528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -4912,7 +1563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -4947,7 +1598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -4982,7 +1633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -5017,7 +1668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -5052,7 +1703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -5087,7 +1738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -5129,28 +1780,28 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.265625" customWidth="1"/>
-    <col min="3" max="3" width="14.265625" customWidth="1"/>
-    <col min="4" max="4" width="21.3984375" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="7" max="7" width="16.59765625" customWidth="1"/>
-    <col min="8" max="8" width="11.1328125" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" customWidth="1"/>
-    <col min="10" max="10" width="13.1328125" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>21</v>
@@ -5170,20 +1821,20 @@
       <c r="G1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -5218,7 +1869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5253,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5288,7 +1939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5323,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5358,7 +2009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -5393,7 +2044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5428,7 +2079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -5463,7 +2114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -5498,7 +2149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -5533,7 +2184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -5568,7 +2219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -5610,61 +2261,61 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.265625" customWidth="1"/>
-    <col min="3" max="3" width="12.86328125" customWidth="1"/>
-    <col min="4" max="4" width="21.3984375" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="7" max="7" width="16.59765625" customWidth="1"/>
-    <col min="8" max="8" width="14.59765625" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" customWidth="1"/>
-    <col min="10" max="10" width="13.1328125" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -5699,7 +2350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5734,7 +2385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5769,7 +2420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5804,7 +2455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5839,7 +2490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -5874,7 +2525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5909,7 +2560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -5944,7 +2595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -5979,7 +2630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -6014,7 +2665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -6049,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -6091,61 +2742,61 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.265625" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" customWidth="1"/>
-    <col min="4" max="4" width="21.3984375" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="7" max="7" width="16.59765625" customWidth="1"/>
-    <col min="8" max="8" width="11.1328125" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" customWidth="1"/>
-    <col min="10" max="10" width="13.1328125" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -6180,7 +2831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6215,7 +2866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6250,7 +2901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -6285,7 +2936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6320,7 +2971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -6355,7 +3006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6390,7 +3041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -6425,7 +3076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -6460,7 +3111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -6495,7 +3146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -6530,7 +3181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -6572,33 +3223,33 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.265625" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="21.3984375" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="7" max="7" width="16.59765625" customWidth="1"/>
-    <col min="8" max="8" width="11.1328125" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" customWidth="1"/>
-    <col min="10" max="10" width="13.1328125" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -6607,26 +3258,26 @@
       <c r="E1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -6661,7 +3312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6696,7 +3347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6731,7 +3382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -6766,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6801,7 +3452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -6836,7 +3487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6871,7 +3522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -6906,7 +3557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -6941,7 +3592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -6976,7 +3627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -7011,7 +3662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -7053,36 +3704,36 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.265625" customWidth="1"/>
-    <col min="3" max="3" width="13.265625" customWidth="1"/>
-    <col min="4" max="4" width="21.3984375" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="7" max="7" width="16.59765625" customWidth="1"/>
-    <col min="8" max="8" width="11.1328125" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" customWidth="1"/>
-    <col min="10" max="10" width="13.1328125" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -7094,20 +3745,20 @@
       <c r="G1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -7142,7 +3793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7177,7 +3828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -7212,7 +3863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -7247,7 +3898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7282,7 +3933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -7317,7 +3968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -7352,7 +4003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -7387,7 +4038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -7422,7 +4073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -7457,7 +4108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -7492,7 +4143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -7534,83 +4185,109 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:Y13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="5" max="5" width="13.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.265625" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="12.73046875" customWidth="1"/>
-    <col min="10" max="10" width="15.73046875" customWidth="1"/>
-    <col min="11" max="11" width="16.1328125" customWidth="1"/>
-    <col min="12" max="12" width="20.73046875" customWidth="1"/>
-    <col min="13" max="13" width="13.73046875" customWidth="1"/>
-    <col min="14" max="14" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.1328125" customWidth="1"/>
-    <col min="16" max="16" width="17.1328125" customWidth="1"/>
-    <col min="17" max="17" width="15.59765625" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="23" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="13" max="13" width="20.7109375" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.140625" customWidth="1"/>
+    <col min="17" max="17" width="17.140625" customWidth="1"/>
+    <col min="18" max="18" width="15.5703125" customWidth="1"/>
+    <col min="19" max="24" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="5" customFormat="1" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:25" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="D1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="G1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="L1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" s="6" t="s">
+      <c r="O1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="P1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -7662,8 +4339,32 @@
       <c r="Q2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7715,8 +4416,32 @@
       <c r="Q3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -7768,8 +4493,32 @@
       <c r="Q4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -7821,8 +4570,32 @@
       <c r="Q5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7874,8 +4647,32 @@
       <c r="Q6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -7927,8 +4724,32 @@
       <c r="Q7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -7980,8 +4801,32 @@
       <c r="Q8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -8033,8 +4878,32 @@
       <c r="Q9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -8086,8 +4955,32 @@
       <c r="Q10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -8139,8 +5032,32 @@
       <c r="Q11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -8192,8 +5109,32 @@
       <c r="Q12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -8243,6 +5184,30 @@
         <v>0</v>
       </c>
       <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
         <v>0</v>
       </c>
     </row>
@@ -8253,27 +5218,27 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.1328125" customWidth="1"/>
-    <col min="3" max="3" width="16.73046875" customWidth="1"/>
-    <col min="4" max="4" width="16.86328125" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="7" max="7" width="14.73046875" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="24.73046875" customWidth="1"/>
-    <col min="10" max="10" width="22.86328125" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.85546875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>21</v>
@@ -8294,19 +5259,19 @@
         <v>20</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -8341,7 +5306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -8376,7 +5341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -8411,7 +5376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -8446,7 +5411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -8481,7 +5446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -8516,7 +5481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -8551,7 +5516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -8586,7 +5551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -8621,7 +5586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -8656,7 +5621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -8691,7 +5656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>

--- a/InputData/fuels/PEIIR/Pollutant Emissions Intensity Improvement Rate.xlsx
+++ b/InputData/fuels/PEIIR/Pollutant Emissions Intensity Improvement Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\fuels\PEIIR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndiaEPS/Shared Documents/Completed EPS Variables/fuels/PEIIR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E3BD0C-A423-4B33-9496-E16F34203A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{81901112-71FD-4606-9377-0C00AA36FDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21279A80-071F-48E8-B8BB-23C3730904E3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="783" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="1080" windowWidth="14610" windowHeight="15585" tabRatio="783" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -29,133 +29,47 @@
     <definedName name="HHV_Adjust">About!#REF!</definedName>
     <definedName name="use_lifecycle_biofuel_EIs">About!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="74">
   <si>
+    <t>PEIIR Transportation Fuel Pollutant Emissions Intensity Improvement Rate</t>
+  </si>
+  <si>
+    <t>PEIIR Electricity Fuel Pollutant Emissions Intensity Improvement Rate</t>
+  </si>
+  <si>
+    <t>PEIIR Buildings Fuel Pollutant Emissions Intensity Improvement Rate</t>
+  </si>
+  <si>
+    <t>PEIIR Industrial Fuel Pollutant Emissions Intensity Improvement Rate</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
     <t>Notes:</t>
   </si>
   <si>
-    <t>VOC</t>
-  </si>
-  <si>
-    <t>CO</t>
-  </si>
-  <si>
-    <t>NOx</t>
-  </si>
-  <si>
-    <t>PM10</t>
-  </si>
-  <si>
-    <t>SOx</t>
-  </si>
-  <si>
-    <t>BC</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>CH4</t>
-  </si>
-  <si>
-    <t>N2O</t>
-  </si>
-  <si>
-    <t>CO2</t>
-  </si>
-  <si>
-    <t>PM25</t>
-  </si>
-  <si>
-    <t>F gases</t>
-  </si>
-  <si>
-    <t>coal</t>
-  </si>
-  <si>
-    <t>natural gas</t>
-  </si>
-  <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>solar PV</t>
-  </si>
-  <si>
-    <t>solar thermal</t>
-  </si>
-  <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t>electricity</t>
-  </si>
-  <si>
-    <t>petroleum diesel</t>
-  </si>
-  <si>
-    <t>heat</t>
-  </si>
-  <si>
-    <t>petroleum gasoline</t>
-  </si>
-  <si>
-    <t>biofuel gasoline</t>
-  </si>
-  <si>
-    <t>biofuel diesel</t>
-  </si>
-  <si>
-    <t>jet fuel</t>
-  </si>
-  <si>
-    <t>geothermal</t>
-  </si>
-  <si>
-    <t>petroleum</t>
-  </si>
-  <si>
-    <t>natural gas peaker</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
-    <t>lignite</t>
-  </si>
-  <si>
-    <t>offshore wind</t>
-  </si>
-  <si>
-    <t>PEIIR Transportation Fuel Pollutant Emissions Intensity Improvement Rate</t>
-  </si>
-  <si>
-    <t>PEIIR Electricity Fuel Pollutant Emissions Intensity Improvement Rate</t>
-  </si>
-  <si>
-    <t>PEIIR Buildings Fuel Pollutant Emissions Intensity Improvement Rate</t>
-  </si>
-  <si>
-    <t>PEIIR Industrial Fuel Pollutant Emissions Intensity Improvement Rate</t>
-  </si>
-  <si>
-    <t>none needed for U.S. model</t>
-  </si>
-  <si>
     <t>This variable specifies the annual improvement rate in emissions intensities of different</t>
   </si>
   <si>
@@ -166,6 +80,12 @@
   </si>
   <si>
     <t>more PM2.5, PM10, BC, and OC in later years of a model run.</t>
+  </si>
+  <si>
+    <t>Annual improvement rates are specified as positive decimals.  For example, an</t>
+  </si>
+  <si>
+    <t>improvement rate of 1% per year would be entered as: 0.01</t>
   </si>
   <si>
     <r>
@@ -194,91 +114,187 @@
     </r>
   </si>
   <si>
+    <t>it be used to represent carbon capture.  Those things are handled elsewhere in the EPS.</t>
+  </si>
+  <si>
+    <t>Therefore, the "CO2" improvement rate should typically be set to zero for all fuels and technologies.</t>
+  </si>
+  <si>
+    <t>An exception would be if the underlying fuel becomes less carbon-intensive</t>
+  </si>
+  <si>
+    <t>over time while remaining the same EPS fuel type.  For example, the EPS fuel</t>
+  </si>
+  <si>
     <t>type "hard coal" may be a mix of anthracite, bituminous, and sub-bituminous coal.</t>
   </si>
   <si>
+    <t>If the mix of hard coal is expected to shift increasingly toward anthracite, which has more</t>
+  </si>
+  <si>
     <t>energy per unit CO2, you could represent this as an improvement rate in the</t>
   </si>
   <si>
     <t>CO2 emissions intensity of the "hard coal" fuel.</t>
   </si>
   <si>
-    <t>it be used to represent carbon capture.  Those things are handled elsewhere in the EPS.</t>
-  </si>
-  <si>
-    <t>Therefore, the "CO2" improvement rate should typically be set to zero for all fuels and technologies.</t>
-  </si>
-  <si>
-    <t>If the mix of hard coal is expected to shift increasingly toward anthracite, which has more</t>
-  </si>
-  <si>
     <t>This variable affects emissions from combustion of fuels, not process emissions.</t>
   </si>
   <si>
-    <t>The U.S. EPS does not assume any improvement in pollutant emissions intensities over time,</t>
-  </si>
-  <si>
     <t>so all rates are set to zero.</t>
   </si>
   <si>
+    <t>Improvement Rate (dimensionless)</t>
+  </si>
+  <si>
+    <t>electricity</t>
+  </si>
+  <si>
+    <t>natural gas</t>
+  </si>
+  <si>
+    <t>petroleum gasoline</t>
+  </si>
+  <si>
+    <t>petroleum diesel</t>
+  </si>
+  <si>
+    <t>biofuel gasoline</t>
+  </si>
+  <si>
+    <t>biofuel diesel</t>
+  </si>
+  <si>
+    <t>jet fuel</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil</t>
+  </si>
+  <si>
+    <t>LPG propane or butane</t>
+  </si>
+  <si>
+    <t>hydrogen</t>
+  </si>
+  <si>
+    <t>CO2</t>
+  </si>
+  <si>
+    <t>VOC</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>NOx</t>
+  </si>
+  <si>
+    <t>PM10</t>
+  </si>
+  <si>
+    <t>PM25</t>
+  </si>
+  <si>
+    <t>SOx</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>CH4</t>
+  </si>
+  <si>
+    <t>N2O</t>
+  </si>
+  <si>
+    <t>F gases</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>solar PV</t>
+  </si>
+  <si>
+    <t>solar thermal</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>petroleum</t>
+  </si>
+  <si>
+    <t>natural gas peaker</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>offshore wind</t>
+  </si>
+  <si>
+    <t>crude oil</t>
+  </si>
+  <si>
+    <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
+  </si>
+  <si>
+    <t>coal</t>
+  </si>
+  <si>
+    <t>heat</t>
+  </si>
+  <si>
     <t>kerosene</t>
   </si>
   <si>
-    <t>heavy or residual fuel oil</t>
-  </si>
-  <si>
-    <t>LPG propane or butane</t>
-  </si>
-  <si>
-    <t>hydrogen</t>
-  </si>
-  <si>
-    <t>crude oil</t>
-  </si>
-  <si>
-    <t>An exception would be if the underlying fuel becomes less carbon-intensive</t>
-  </si>
-  <si>
-    <t>over time while remaining the same EPS fuel type.  For example, the EPS fuel</t>
-  </si>
-  <si>
-    <t>improvement rate of 1% per year would be entered as: 0.01</t>
-  </si>
-  <si>
-    <t>Annual improvement rates are specified as positive decimals.  For example, an</t>
-  </si>
-  <si>
-    <t>municipal solid waste</t>
-  </si>
-  <si>
-    <t>Improvement Rate (dimensionless)</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
-  </si>
-  <si>
-    <t>hard coal w CCS</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle w CCS</t>
-  </si>
-  <si>
-    <t>biomass w CCS</t>
-  </si>
-  <si>
-    <t>lignite w CCS</t>
-  </si>
-  <si>
-    <t>small modular reactor</t>
-  </si>
-  <si>
-    <t>hydrogen combustion turbine</t>
-  </si>
-  <si>
-    <t>hydrogen combined cycle</t>
+    <t xml:space="preserve">none needed </t>
+  </si>
+  <si>
+    <t>The EPS does not assume any improvement in pollutant emissions intensities over time,</t>
   </si>
 </sst>
 </file>
@@ -683,133 +699,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" customWidth="1"/>
     <col min="2" max="2" width="73" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -824,57 +840,57 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7265625" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" customWidth="1"/>
+    <col min="9" max="9" width="15.26953125" customWidth="1"/>
+    <col min="10" max="10" width="13.54296875" customWidth="1"/>
+    <col min="11" max="11" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -907,9 +923,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -942,9 +958,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -977,9 +993,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1012,9 +1028,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1047,9 +1063,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1082,9 +1098,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1117,9 +1133,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1152,9 +1168,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1187,9 +1203,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1222,9 +1238,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1257,9 +1273,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1304,58 +1320,58 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1388,9 +1404,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1423,9 +1439,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1458,9 +1474,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1493,9 +1509,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1528,9 +1544,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1563,9 +1579,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1598,9 +1614,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1633,9 +1649,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1668,9 +1684,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1703,9 +1719,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1738,9 +1754,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1785,58 +1801,58 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
+    <col min="3" max="3" width="14.26953125" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1869,9 +1885,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1904,9 +1920,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1939,9 +1955,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1974,9 +1990,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2009,9 +2025,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2044,9 +2060,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2079,9 +2095,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2114,9 +2130,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2149,9 +2165,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2184,9 +2200,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2219,9 +2235,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2266,58 +2282,58 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2350,9 +2366,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2385,9 +2401,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2420,9 +2436,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2455,9 +2471,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2490,9 +2506,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2525,9 +2541,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2560,9 +2576,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2595,9 +2611,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2630,9 +2646,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2665,9 +2681,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2700,9 +2716,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2747,58 +2763,58 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2831,9 +2847,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2866,9 +2882,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2901,9 +2917,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2936,9 +2952,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2971,9 +2987,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3006,9 +3022,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3041,9 +3057,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3076,9 +3092,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3111,9 +3127,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3146,9 +3162,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3181,9 +3197,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3228,58 +3244,58 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3312,9 +3328,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3347,9 +3363,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3382,9 +3398,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3417,9 +3433,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3452,9 +3468,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3487,9 +3503,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3522,9 +3538,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3557,9 +3573,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3592,9 +3608,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3627,9 +3643,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3662,9 +3678,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3709,58 +3725,58 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3793,9 +3809,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3828,9 +3844,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3863,9 +3879,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3898,9 +3914,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3933,9 +3949,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3968,9 +3984,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4003,9 +4019,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4038,9 +4054,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4073,9 +4089,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -4108,9 +4124,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4143,9 +4159,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4190,107 +4206,107 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="23" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
-    <col min="13" max="13" width="20.7109375" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.140625" customWidth="1"/>
-    <col min="17" max="17" width="17.140625" customWidth="1"/>
-    <col min="18" max="18" width="15.5703125" customWidth="1"/>
-    <col min="19" max="24" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.7265625" customWidth="1"/>
+    <col min="11" max="11" width="15.7265625" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" customWidth="1"/>
+    <col min="13" max="13" width="20.7265625" customWidth="1"/>
+    <col min="14" max="14" width="13.7265625" customWidth="1"/>
+    <col min="15" max="15" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" customWidth="1"/>
+    <col min="17" max="17" width="17.1796875" customWidth="1"/>
+    <col min="18" max="18" width="15.54296875" customWidth="1"/>
+    <col min="19" max="24" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O1" s="4" t="s">
+      <c r="X1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>34</v>
       </c>
-      <c r="P1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
       <c r="B2">
         <v>0</v>
       </c>
@@ -4364,9 +4380,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4441,9 +4457,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4518,9 +4534,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4595,9 +4611,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4672,9 +4688,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4749,9 +4765,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4826,9 +4842,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4903,9 +4919,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4980,9 +4996,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -5057,9 +5073,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -5134,9 +5150,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -5223,57 +5239,57 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" customWidth="1"/>
+    <col min="3" max="3" width="16.7265625" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
-    <col min="10" max="10" width="22.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" customWidth="1"/>
+    <col min="9" max="9" width="24.7265625" customWidth="1"/>
+    <col min="10" max="10" width="22.81640625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5306,9 +5322,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5341,9 +5357,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5376,9 +5392,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5411,9 +5427,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5446,9 +5462,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5481,9 +5497,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -5516,9 +5532,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -5551,9 +5567,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -5586,9 +5602,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -5621,9 +5637,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -5656,9 +5672,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -5695,4 +5711,179 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6029DA5-3C43-4F4E-BE77-9E4600C9D251}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACC41120-EF24-4B35-96F4-7911ED5622B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFDD36B5-F500-4B26-A520-0D0FA2F39D05}"/>
 </file>